--- a/final_run_2026/all_subj_methods_anova/rew_lvl_comparisons.xlsx
+++ b/final_run_2026/all_subj_methods_anova/rew_lvl_comparisons.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="5390" uniqueCount="4205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="10078" uniqueCount="4354">
   <si>
     <t>subject level observations</t>
   </si>
@@ -12636,6 +12636,453 @@
   </si>
   <si>
     <t>0.035026</t>
+  </si>
+  <si>
+    <t>20.9571</t>
+  </si>
+  <si>
+    <t>24.5088</t>
+  </si>
+  <si>
+    <t>29.8973</t>
+  </si>
+  <si>
+    <t>30.8119</t>
+  </si>
+  <si>
+    <t>51.0315</t>
+  </si>
+  <si>
+    <t>35.4144</t>
+  </si>
+  <si>
+    <t>27.5676</t>
+  </si>
+  <si>
+    <t>32.1963</t>
+  </si>
+  <si>
+    <t>35.125</t>
+  </si>
+  <si>
+    <t>33.2576</t>
+  </si>
+  <si>
+    <t>43.5333</t>
+  </si>
+  <si>
+    <t>38.1277</t>
+  </si>
+  <si>
+    <t>56.209</t>
+  </si>
+  <si>
+    <t>38.2941</t>
+  </si>
+  <si>
+    <t>42.95</t>
+  </si>
+  <si>
+    <t>44.4487</t>
+  </si>
+  <si>
+    <t>54.4126</t>
+  </si>
+  <si>
+    <t>50.7778</t>
+  </si>
+  <si>
+    <t>49.0866</t>
+  </si>
+  <si>
+    <t>54.165</t>
+  </si>
+  <si>
+    <t>60.3333</t>
+  </si>
+  <si>
+    <t>47.1574</t>
+  </si>
+  <si>
+    <t>52.6702</t>
+  </si>
+  <si>
+    <t>48.7374</t>
+  </si>
+  <si>
+    <t>58.3791</t>
+  </si>
+  <si>
+    <t>55.4746</t>
+  </si>
+  <si>
+    <t>59.0479</t>
+  </si>
+  <si>
+    <t>48.1053</t>
+  </si>
+  <si>
+    <t>59.1463</t>
+  </si>
+  <si>
+    <t>50.9159</t>
+  </si>
+  <si>
+    <t>59.2727</t>
+  </si>
+  <si>
+    <t>50.8056</t>
+  </si>
+  <si>
+    <t>1.6382</t>
+  </si>
+  <si>
+    <t>1.2173</t>
+  </si>
+  <si>
+    <t>1.4047</t>
+  </si>
+  <si>
+    <t>1.6408</t>
+  </si>
+  <si>
+    <t>1.4015</t>
+  </si>
+  <si>
+    <t>1.6215</t>
+  </si>
+  <si>
+    <t>1.4846</t>
+  </si>
+  <si>
+    <t>1.5461</t>
+  </si>
+  <si>
+    <t>1.2419</t>
+  </si>
+  <si>
+    <t>1.517</t>
+  </si>
+  <si>
+    <t>1.5796</t>
+  </si>
+  <si>
+    <t>1.2982</t>
+  </si>
+  <si>
+    <t>1.4352</t>
+  </si>
+  <si>
+    <t>1.7582</t>
+  </si>
+  <si>
+    <t>1.6186</t>
+  </si>
+  <si>
+    <t>1.3353</t>
+  </si>
+  <si>
+    <t>1.4758</t>
+  </si>
+  <si>
+    <t>1.6519</t>
+  </si>
+  <si>
+    <t>1.3519</t>
+  </si>
+  <si>
+    <t>1.6301</t>
+  </si>
+  <si>
+    <t>1.5385</t>
+  </si>
+  <si>
+    <t>1.6258</t>
+  </si>
+  <si>
+    <t>1.5264</t>
+  </si>
+  <si>
+    <t>1.2919</t>
+  </si>
+  <si>
+    <t>1.403</t>
+  </si>
+  <si>
+    <t>1.6087</t>
+  </si>
+  <si>
+    <t>1.4732</t>
+  </si>
+  <si>
+    <t>1.5977</t>
+  </si>
+  <si>
+    <t>1.4917</t>
+  </si>
+  <si>
+    <t>1.6397</t>
+  </si>
+  <si>
+    <t>2.9322</t>
+  </si>
+  <si>
+    <t>3.1552</t>
+  </si>
+  <si>
+    <t>2.9372</t>
+  </si>
+  <si>
+    <t>2.8528</t>
+  </si>
+  <si>
+    <t>2.93</t>
+  </si>
+  <si>
+    <t>2.6951</t>
+  </si>
+  <si>
+    <t>3.1144</t>
+  </si>
+  <si>
+    <t>2.9494</t>
+  </si>
+  <si>
+    <t>3.1486</t>
+  </si>
+  <si>
+    <t>2.9587</t>
+  </si>
+  <si>
+    <t>2.8496</t>
+  </si>
+  <si>
+    <t>2.9153</t>
+  </si>
+  <si>
+    <t>2.6874</t>
+  </si>
+  <si>
+    <t>3.0903</t>
+  </si>
+  <si>
+    <t>2.743</t>
+  </si>
+  <si>
+    <t>2.9493</t>
+  </si>
+  <si>
+    <t>3.1685</t>
+  </si>
+  <si>
+    <t>2.9505</t>
+  </si>
+  <si>
+    <t>2.8416</t>
+  </si>
+  <si>
+    <t>2.9259</t>
+  </si>
+  <si>
+    <t>2.7111</t>
+  </si>
+  <si>
+    <t>3.1148</t>
+  </si>
+  <si>
+    <t>2.7667</t>
+  </si>
+  <si>
+    <t>2.9623</t>
+  </si>
+  <si>
+    <t>3.1777</t>
+  </si>
+  <si>
+    <t>2.9249</t>
+  </si>
+  <si>
+    <t>2.8472</t>
+  </si>
+  <si>
+    <t>2.7119</t>
+  </si>
+  <si>
+    <t>3.1273</t>
+  </si>
+  <si>
+    <t>2.7597</t>
+  </si>
+  <si>
+    <t>149.85271</t>
+  </si>
+  <si>
+    <t>227.53571</t>
+  </si>
+  <si>
+    <t>193.89231</t>
+  </si>
+  <si>
+    <t>137.80198</t>
+  </si>
+  <si>
+    <t>423.28</t>
+  </si>
+  <si>
+    <t>273.01905</t>
+  </si>
+  <si>
+    <t>323.72973</t>
+  </si>
+  <si>
+    <t>305.1028</t>
+  </si>
+  <si>
+    <t>115.5299</t>
+  </si>
+  <si>
+    <t>200.3485</t>
+  </si>
+  <si>
+    <t>181.6308</t>
+  </si>
+  <si>
+    <t>176.8617</t>
+  </si>
+  <si>
+    <t>350.2636</t>
+  </si>
+  <si>
+    <t>266.0761</t>
+  </si>
+  <si>
+    <t>311.1923</t>
+  </si>
+  <si>
+    <t>249.2949</t>
+  </si>
+  <si>
+    <t>180.2031</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>198.8067</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>328.0932</t>
+  </si>
+  <si>
+    <t>296.7745</t>
+  </si>
+  <si>
+    <t>247.9355</t>
+  </si>
+  <si>
+    <t>324.5612</t>
+  </si>
+  <si>
+    <t>194.3162</t>
+  </si>
+  <si>
+    <t>242.2034</t>
+  </si>
+  <si>
+    <t>163.8571</t>
+  </si>
+  <si>
+    <t>132.5526</t>
+  </si>
+  <si>
+    <t>347.8158</t>
+  </si>
+  <si>
+    <t>342.9286</t>
+  </si>
+  <si>
+    <t>268.1364</t>
+  </si>
+  <si>
+    <t>366.463</t>
+  </si>
+  <si>
+    <t>1.4884</t>
+  </si>
+  <si>
+    <t>2.0357</t>
+  </si>
+  <si>
+    <t>2.0231</t>
+  </si>
+  <si>
+    <t>1.8812</t>
+  </si>
+  <si>
+    <t>2.792</t>
+  </si>
+  <si>
+    <t>2.0762</t>
+  </si>
+  <si>
+    <t>2.8243</t>
+  </si>
+  <si>
+    <t>2.2523</t>
+  </si>
+  <si>
+    <t>1.1795</t>
+  </si>
+  <si>
+    <t>2.0154</t>
+  </si>
+  <si>
+    <t>2.4961</t>
+  </si>
+  <si>
+    <t>2.8718</t>
+  </si>
+  <si>
+    <t>1.7578</t>
+  </si>
+  <si>
+    <t>2.6481</t>
+  </si>
+  <si>
+    <t>1.9076</t>
+  </si>
+  <si>
+    <t>1.7767</t>
+  </si>
+  <si>
+    <t>2.2373</t>
+  </si>
+  <si>
+    <t>2.098</t>
+  </si>
+  <si>
+    <t>2.4082</t>
+  </si>
+  <si>
+    <t>1.8603</t>
+  </si>
+  <si>
+    <t>2.4576</t>
+  </si>
+  <si>
+    <t>1.5614</t>
+  </si>
+  <si>
+    <t>2.7193</t>
+  </si>
+  <si>
+    <t>2.5455</t>
+  </si>
+  <si>
+    <t>2.7778</t>
   </si>
 </sst>
 </file>
@@ -12757,7 +13204,7 @@
         <v>852</v>
       </c>
       <c r="H2" s="0">
-        <v>58142.577655545749</v>
+        <v>58343.421709572227</v>
       </c>
       <c r="I2" s="0">
         <v>3</v>
@@ -12766,13 +13213,13 @@
         <v>0</v>
       </c>
       <c r="K2" s="0">
-        <v>19380.859218515248</v>
+        <v>19447.807236524077</v>
       </c>
       <c r="L2" s="0">
-        <v>75.52129009808786</v>
+        <v>75.739256368480994</v>
       </c>
       <c r="M2" s="0">
-        <v>6.1773209139159366e-44</v>
+        <v>4.7431931079273809e-44</v>
       </c>
       <c r="O2" s="0" t="s">
         <v>872</v>
@@ -12795,7 +13242,7 @@
         <v>853</v>
       </c>
       <c r="H3" s="0">
-        <v>250725.31774677426</v>
+        <v>250867.36497179439</v>
       </c>
       <c r="I3" s="0">
         <v>977</v>
@@ -12804,7 +13251,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="0">
-        <v>256.62775613794707</v>
+        <v>256.77314736109969</v>
       </c>
       <c r="L3" s="0"/>
       <c r="M3" s="0"/>
@@ -12814,22 +13261,22 @@
     </row>
     <row r="4">
       <c r="B4" s="0" t="s">
-        <v>4</v>
+        <v>4205</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>235</v>
+        <v>4213</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>451</v>
+        <v>4221</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>660</v>
+        <v>4229</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>854</v>
       </c>
       <c r="H4" s="0">
-        <v>308867.89540232002</v>
+        <v>309210.78668136662</v>
       </c>
       <c r="I4" s="0">
         <v>980</v>
@@ -12960,16 +13407,16 @@
         <v>863</v>
       </c>
       <c r="I11" s="0">
-        <v>-10.490790876974284</v>
+        <v>-10.501793043827144</v>
       </c>
       <c r="J11" s="0">
-        <v>-6.7723844061301861</v>
+        <v>-6.782333399462658</v>
       </c>
       <c r="K11" s="0">
-        <v>-3.0539779352860887</v>
+        <v>-3.0628737550981726</v>
       </c>
       <c r="L11" s="0">
-        <v>1.7119500375894392e-05</v>
+        <v>1.6663921191486518e-05</v>
       </c>
     </row>
     <row r="12">
@@ -12992,13 +13439,13 @@
         <v>864</v>
       </c>
       <c r="I12" s="0">
-        <v>-20.055906717740235</v>
+        <v>-20.08196992577242</v>
       </c>
       <c r="J12" s="0">
-        <v>-16.329919389952707</v>
+        <v>-16.354927277319518</v>
       </c>
       <c r="K12" s="0">
-        <v>-12.603932062165176</v>
+        <v>-12.627884628866617</v>
       </c>
       <c r="L12" s="0">
         <v>0</v>
@@ -13024,13 +13471,13 @@
         <v>866</v>
       </c>
       <c r="I13" s="0">
-        <v>-23.111406360128292</v>
+        <v>-23.147200619372796</v>
       </c>
       <c r="J13" s="0">
-        <v>-19.39674998810996</v>
+        <v>-19.431492135983902</v>
       </c>
       <c r="K13" s="0">
-        <v>-15.682093616091629</v>
+        <v>-15.715783652595007</v>
       </c>
       <c r="L13" s="0">
         <v>0</v>
@@ -13056,16 +13503,16 @@
         <v>864</v>
       </c>
       <c r="I14" s="0">
-        <v>-13.275941454666617</v>
+        <v>-13.292053522221345</v>
       </c>
       <c r="J14" s="0">
-        <v>-9.5575349838225208</v>
+        <v>-9.5725938778568604</v>
       </c>
       <c r="K14" s="0">
-        <v>-5.8391285129784247</v>
+        <v>-5.8531342334923764</v>
       </c>
       <c r="L14" s="0">
-        <v>2.3065379559545773e-10</v>
+        <v>2.1756485054180709e-10</v>
       </c>
     </row>
     <row r="15">
@@ -13088,16 +13535,16 @@
         <v>866</v>
       </c>
       <c r="I15" s="0">
-        <v>-16.331417925521521</v>
+        <v>-16.357261037725642</v>
       </c>
       <c r="J15" s="0">
-        <v>-12.624365581979774</v>
+        <v>-12.649158736521244</v>
       </c>
       <c r="K15" s="0">
-        <v>-8.9173132384380249</v>
+        <v>-8.9410564353168454</v>
       </c>
       <c r="L15" s="0">
-        <v>4.4391008008380753e-18</v>
+        <v>3.837394218267276e-18</v>
       </c>
     </row>
     <row r="16">
@@ -13120,16 +13567,16 @@
         <v>866</v>
       </c>
       <c r="I16" s="0">
-        <v>-6.7814869701755871</v>
+        <v>-6.7922733420532815</v>
       </c>
       <c r="J16" s="0">
-        <v>-3.066830598157253</v>
+        <v>-3.0765648586643835</v>
       </c>
       <c r="K16" s="0">
-        <v>0.64782577386108153</v>
+        <v>0.63914362472451414</v>
       </c>
       <c r="L16" s="0">
-        <v>0.14637170501086844</v>
+        <v>0.14446415571533752</v>
       </c>
     </row>
     <row r="17">
@@ -13274,16 +13721,16 @@
     </row>
     <row r="27">
       <c r="B27" s="0" t="s">
-        <v>27</v>
+        <v>4206</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>254</v>
+        <v>4214</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>469</v>
+        <v>4222</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>676</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="28">
@@ -13648,16 +14095,16 @@
     </row>
     <row r="54">
       <c r="B54" s="0" t="s">
-        <v>2</v>
+        <v>4207</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>276</v>
+        <v>4215</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>493</v>
+        <v>4223</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>697</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="55">
@@ -13746,16 +14193,16 @@
     </row>
     <row r="61">
       <c r="B61" s="0" t="s">
-        <v>56</v>
+        <v>4208</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>283</v>
+        <v>4216</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>500</v>
+        <v>4224</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>702</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="62">
@@ -15510,16 +15957,16 @@
     </row>
     <row r="189">
       <c r="B189" s="0" t="s">
-        <v>173</v>
+        <v>4209</v>
       </c>
       <c r="C189" s="0" t="s">
-        <v>389</v>
+        <v>4217</v>
       </c>
       <c r="D189" s="0" t="s">
-        <v>604</v>
+        <v>4225</v>
       </c>
       <c r="E189" s="0" t="s">
-        <v>802</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="190">
@@ -15608,16 +16055,16 @@
     </row>
     <row r="196">
       <c r="B196" s="0" t="s">
-        <v>180</v>
+        <v>4210</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>396</v>
+        <v>4218</v>
       </c>
       <c r="D196" s="0" t="s">
-        <v>609</v>
+        <v>4226</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>809</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="197">
@@ -16056,16 +16503,16 @@
     </row>
     <row r="228">
       <c r="B228" s="0" t="s">
-        <v>209</v>
+        <v>4211</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>426</v>
+        <v>4219</v>
       </c>
       <c r="D228" s="0" t="s">
-        <v>636</v>
+        <v>4227</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>834</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="229">
@@ -16336,16 +16783,16 @@
     </row>
     <row r="248">
       <c r="B248" s="0" t="s">
-        <v>229</v>
+        <v>4212</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>445</v>
+        <v>4220</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>655</v>
+        <v>4228</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>848</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="249">
@@ -16464,7 +16911,7 @@
         <v>852</v>
       </c>
       <c r="H2" s="0">
-        <v>0.34332247094976093</v>
+        <v>0.33789525863256548</v>
       </c>
       <c r="I2" s="0">
         <v>3</v>
@@ -16473,13 +16920,13 @@
         <v>0</v>
       </c>
       <c r="K2" s="0">
-        <v>0.11444082364992031</v>
+        <v>0.11263175287752182</v>
       </c>
       <c r="L2" s="0">
-        <v>1.3786576237547128</v>
+        <v>1.3580915012900774</v>
       </c>
       <c r="M2" s="0">
-        <v>0.24803031635198913</v>
+        <v>0.25442400751031091</v>
       </c>
       <c r="O2" s="0" t="s">
         <v>872</v>
@@ -16502,7 +16949,7 @@
         <v>853</v>
       </c>
       <c r="H3" s="0">
-        <v>62.671703523007828</v>
+        <v>62.615054539219713</v>
       </c>
       <c r="I3" s="0">
         <v>755</v>
@@ -16511,7 +16958,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="0">
-        <v>0.083008878838420966</v>
+        <v>0.082933847071814185</v>
       </c>
       <c r="L3" s="0"/>
       <c r="M3" s="0"/>
@@ -16521,22 +16968,22 @@
     </row>
     <row r="4">
       <c r="B4" s="0" t="s">
-        <v>876</v>
+        <v>4237</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>1063</v>
+        <v>4244</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>1240</v>
+        <v>4251</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>1414</v>
+        <v>4259</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>854</v>
       </c>
       <c r="H4" s="0">
-        <v>63.015025993957586</v>
+        <v>62.952949797852277</v>
       </c>
       <c r="I4" s="0">
         <v>758</v>
@@ -16643,16 +17090,16 @@
         <v>863</v>
       </c>
       <c r="I11" s="0">
-        <v>-0.048447548091766629</v>
+        <v>-0.048123992058560897</v>
       </c>
       <c r="J11" s="0">
-        <v>0.027896285939207788</v>
+        <v>0.028185330557273458</v>
       </c>
       <c r="K11" s="0">
-        <v>0.1042401199701822</v>
+        <v>0.10449465317310781</v>
       </c>
       <c r="L11" s="0">
-        <v>0.78397313779334488</v>
+        <v>0.77836982095500062</v>
       </c>
     </row>
     <row r="12">
@@ -16675,16 +17122,16 @@
         <v>864</v>
       </c>
       <c r="I12" s="0">
-        <v>-0.023986001162633511</v>
+        <v>-0.024227017019808464</v>
       </c>
       <c r="J12" s="0">
-        <v>0.052255703494773487</v>
+        <v>0.05198022239028921</v>
       </c>
       <c r="K12" s="0">
-        <v>0.12849740815218047</v>
+        <v>0.12818746180038687</v>
       </c>
       <c r="L12" s="0">
-        <v>0.29242134189947872</v>
+        <v>0.29666968330210386</v>
       </c>
     </row>
     <row r="13">
@@ -16707,16 +17154,16 @@
         <v>866</v>
       </c>
       <c r="I13" s="0">
-        <v>-0.02458825686083857</v>
+        <v>-0.024971214568423813</v>
       </c>
       <c r="J13" s="0">
-        <v>0.050964297843294037</v>
+        <v>0.050547186420305534</v>
       </c>
       <c r="K13" s="0">
-        <v>0.12651685254742664</v>
+        <v>0.1260655874090349</v>
       </c>
       <c r="L13" s="0">
-        <v>0.30648855404293723</v>
+        <v>0.31339326970009196</v>
       </c>
     </row>
     <row r="14">
@@ -16733,16 +17180,16 @@
         <v>864</v>
       </c>
       <c r="I14" s="0">
-        <v>-0.052085330829356236</v>
+        <v>-0.0526152995181879</v>
       </c>
       <c r="J14" s="0">
-        <v>0.024359417555565699</v>
+        <v>0.023794891833015752</v>
       </c>
       <c r="K14" s="0">
-        <v>0.10080416594048763</v>
+        <v>0.1002050831842194</v>
       </c>
       <c r="L14" s="0">
-        <v>0.84569670817591891</v>
+        <v>0.85443336077159049</v>
       </c>
     </row>
     <row r="15">
@@ -16765,16 +17212,16 @@
         <v>866</v>
       </c>
       <c r="I15" s="0">
-        <v>-0.052689433597248453</v>
+        <v>-0.05336134330151808</v>
       </c>
       <c r="J15" s="0">
-        <v>0.02306801190408625</v>
+        <v>0.022361855863032076</v>
       </c>
       <c r="K15" s="0">
-        <v>0.098825457405420952</v>
+        <v>0.098085055027582232</v>
       </c>
       <c r="L15" s="0">
-        <v>0.86254390589579655</v>
+        <v>0.87297583611046436</v>
       </c>
     </row>
     <row r="16">
@@ -16797,16 +17244,16 @@
         <v>866</v>
       </c>
       <c r="I16" s="0">
-        <v>-0.076945930191694545</v>
+        <v>-0.077053360699084056</v>
       </c>
       <c r="J16" s="0">
-        <v>-0.0012914056514794492</v>
+        <v>-0.0014330359699836759</v>
       </c>
       <c r="K16" s="0">
-        <v>0.074363118888735646</v>
+        <v>0.074187288759116704</v>
       </c>
       <c r="L16" s="0">
-        <v>0.99996972822827235</v>
+        <v>0.99995858832210205</v>
       </c>
     </row>
     <row r="17">
@@ -16935,16 +17382,16 @@
     </row>
     <row r="27">
       <c r="B27" s="0" t="s">
-        <v>892</v>
+        <v>4238</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>1078</v>
+        <v>4245</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>1256</v>
+        <v>4252</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>1428</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="28">
@@ -17287,16 +17734,16 @@
     </row>
     <row r="54">
       <c r="B54" s="0" t="s">
-        <v>916</v>
+        <v>4239</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>1101</v>
+        <v>4246</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>1280</v>
+        <v>4253</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>1451</v>
+        <v>4261</v>
       </c>
     </row>
     <row r="55">
@@ -17385,16 +17832,16 @@
     </row>
     <row r="61">
       <c r="B61" s="0" t="s">
-        <v>923</v>
+        <v>4240</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>1108</v>
+        <v>4247</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>1286</v>
+        <v>4254</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>1457</v>
+        <v>4262</v>
       </c>
     </row>
     <row r="62">
@@ -18867,16 +19314,16 @@
     </row>
     <row r="189">
       <c r="B189" s="0" t="s">
-        <v>1010</v>
+        <v>4241</v>
       </c>
       <c r="C189" s="0" t="s">
-        <v>1192</v>
+        <v>4248</v>
       </c>
       <c r="D189" s="0" t="s">
-        <v>1364</v>
+        <v>4255</v>
       </c>
       <c r="E189" s="0" t="s">
-        <v>1544</v>
+        <v>4263</v>
       </c>
     </row>
     <row r="190">
@@ -18957,16 +19404,16 @@
     </row>
     <row r="196">
       <c r="B196" s="0" t="s">
-        <v>1016</v>
+        <v>4242</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>1197</v>
+        <v>4249</v>
       </c>
       <c r="D196" s="0" t="s">
-        <v>1075</v>
+        <v>4256</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>1550</v>
+        <v>4264</v>
       </c>
     </row>
     <row r="197">
@@ -19381,16 +19828,16 @@
     </row>
     <row r="228">
       <c r="B228" s="0" t="s">
-        <v>1045</v>
+        <v>4243</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>1222</v>
+        <v>3482</v>
       </c>
       <c r="D228" s="0" t="s">
-        <v>1395</v>
+        <v>4257</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>1578</v>
+        <v>4265</v>
       </c>
     </row>
     <row r="229">
@@ -19623,16 +20070,16 @@
     </row>
     <row r="248">
       <c r="B248" s="0" t="s">
-        <v>1060</v>
+        <v>3585</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>1237</v>
+        <v>4250</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>1411</v>
+        <v>4258</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>1592</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="249">
@@ -19681,7 +20128,7 @@
     <col min="10" max="10" width="15.21875" customWidth="true"/>
     <col min="11" max="11" width="13.5546875" customWidth="true"/>
     <col min="12" max="12" width="12.5546875" customWidth="true"/>
-    <col min="13" max="13" width="11.5546875" customWidth="true"/>
+    <col min="13" max="13" width="12.5546875" customWidth="true"/>
     <col min="15" max="15" width="36.44140625" customWidth="true"/>
   </cols>
   <sheetData>
@@ -19735,7 +20182,7 @@
         <v>852</v>
       </c>
       <c r="H2" s="0">
-        <v>0.013596828660876895</v>
+        <v>0.014696272925131797</v>
       </c>
       <c r="I2" s="0">
         <v>3</v>
@@ -19744,13 +20191,13 @@
         <v>0</v>
       </c>
       <c r="K2" s="0">
-        <v>0.0045322762202922983</v>
+        <v>0.0048987576417105988</v>
       </c>
       <c r="L2" s="0">
-        <v>0.039769206313793465</v>
+        <v>0.043002600997178342</v>
       </c>
       <c r="M2" s="0">
-        <v>0.98941541299312696</v>
+        <v>0.98813312610186721</v>
       </c>
       <c r="O2" s="0" t="s">
         <v>872</v>
@@ -19773,7 +20220,7 @@
         <v>853</v>
       </c>
       <c r="H3" s="0">
-        <v>92.653107985703784</v>
+        <v>92.615094676995113</v>
       </c>
       <c r="I3" s="0">
         <v>813</v>
@@ -19782,7 +20229,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="0">
-        <v>0.11396446246704033</v>
+        <v>0.11391770562976029</v>
       </c>
       <c r="L3" s="0"/>
       <c r="M3" s="0"/>
@@ -19792,22 +20239,22 @@
     </row>
     <row r="4">
       <c r="B4" s="0" t="s">
-        <v>1595</v>
+        <v>4267</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>1796</v>
+        <v>4274</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>1994</v>
+        <v>4282</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>2183</v>
+        <v>4290</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>854</v>
       </c>
       <c r="H4" s="0">
-        <v>92.666704814364664</v>
+        <v>92.629790949920249</v>
       </c>
       <c r="I4" s="0">
         <v>816</v>
@@ -19920,16 +20367,16 @@
         <v>863</v>
       </c>
       <c r="I11" s="0">
-        <v>-0.082660700580302046</v>
+        <v>-0.082406444608195059</v>
       </c>
       <c r="J11" s="0">
-        <v>0.003317489914935301</v>
+        <v>0.0035541067011322092</v>
       </c>
       <c r="K11" s="0">
-        <v>0.089295680410172648</v>
+        <v>0.089514658010459477</v>
       </c>
       <c r="L11" s="0">
-        <v>0.99965143595311479</v>
+        <v>0.99957137784118555</v>
       </c>
     </row>
     <row r="12">
@@ -19952,16 +20399,16 @@
         <v>864</v>
       </c>
       <c r="I12" s="0">
-        <v>-0.087706668549878963</v>
+        <v>-0.087987755734846018</v>
       </c>
       <c r="J12" s="0">
-        <v>-0.0017284780546416023</v>
+        <v>-0.002027204425518736</v>
       </c>
       <c r="K12" s="0">
-        <v>0.084249712440595759</v>
+        <v>0.083933346883808546</v>
       </c>
       <c r="L12" s="0">
-        <v>0.99995056448560227</v>
+        <v>0.99992023148908871</v>
       </c>
     </row>
     <row r="13">
@@ -19984,16 +20431,16 @@
         <v>866</v>
       </c>
       <c r="I13" s="0">
-        <v>-0.093656123673420952</v>
+        <v>-0.093859587923351195</v>
       </c>
       <c r="J13" s="0">
-        <v>-0.0078863579946504281</v>
+        <v>-0.0081074186702969619</v>
       </c>
       <c r="K13" s="0">
-        <v>0.077883407684120096</v>
+        <v>0.077644750582757271</v>
       </c>
       <c r="L13" s="0">
-        <v>0.99536367581911045</v>
+        <v>0.99496567436049488</v>
       </c>
     </row>
     <row r="14">
@@ -20016,16 +20463,16 @@
         <v>864</v>
       </c>
       <c r="I14" s="0">
-        <v>-0.090918469192540166</v>
+        <v>-0.091436194846792732</v>
       </c>
       <c r="J14" s="0">
-        <v>-0.0050459679695769033</v>
+        <v>-0.0055813111266509452</v>
       </c>
       <c r="K14" s="0">
-        <v>0.08082653325338636</v>
+        <v>0.080273572593490841</v>
       </c>
       <c r="L14" s="0">
-        <v>0.99877488147591109</v>
+        <v>0.99834426485076722</v>
       </c>
     </row>
     <row r="15">
@@ -20048,16 +20495,16 @@
         <v>866</v>
       </c>
       <c r="I15" s="0">
-        <v>-0.096867667168615432</v>
+        <v>-0.097307769940587249</v>
       </c>
       <c r="J15" s="0">
-        <v>-0.011203847909585729</v>
+        <v>-0.011661525371429171</v>
       </c>
       <c r="K15" s="0">
-        <v>0.074459971349443974</v>
+        <v>0.073984719197728907</v>
       </c>
       <c r="L15" s="0">
-        <v>0.98693767818448863</v>
+        <v>0.98531324847801083</v>
       </c>
     </row>
     <row r="16">
@@ -20080,16 +20527,16 @@
         <v>866</v>
       </c>
       <c r="I16" s="0">
-        <v>-0.09182169919903857</v>
+        <v>-0.091726458813936346</v>
       </c>
       <c r="J16" s="0">
-        <v>-0.0061578799400088258</v>
+        <v>-0.0060802142447782259</v>
       </c>
       <c r="K16" s="0">
-        <v>0.079505939319020918</v>
+        <v>0.079566030324379894</v>
       </c>
       <c r="L16" s="0">
-        <v>0.99776658658553008</v>
+        <v>0.99784803058097893</v>
       </c>
     </row>
     <row r="17">
@@ -20218,16 +20665,16 @@
     </row>
     <row r="27">
       <c r="B27" s="0" t="s">
-        <v>1613</v>
+        <v>4268</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>1814</v>
+        <v>4275</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>2012</v>
+        <v>4283</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>2201</v>
+        <v>4291</v>
       </c>
     </row>
     <row r="28">
@@ -20576,16 +21023,16 @@
     </row>
     <row r="54">
       <c r="B54" s="0" t="s">
-        <v>1637</v>
+        <v>4269</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>1838</v>
+        <v>4276</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>2036</v>
+        <v>4284</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>2224</v>
+        <v>4292</v>
       </c>
     </row>
     <row r="55">
@@ -20674,16 +21121,16 @@
     </row>
     <row r="61">
       <c r="B61" s="0" t="s">
-        <v>1644</v>
+        <v>4270</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>1845</v>
+        <v>4277</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>2040</v>
+        <v>4285</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>2231</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="62">
@@ -22232,16 +22679,16 @@
     </row>
     <row r="189">
       <c r="B189" s="0" t="s">
-        <v>1741</v>
+        <v>4271</v>
       </c>
       <c r="C189" s="0" t="s">
-        <v>1940</v>
+        <v>4278</v>
       </c>
       <c r="D189" s="0" t="s">
-        <v>2133</v>
+        <v>4286</v>
       </c>
       <c r="E189" s="0" t="s">
-        <v>2326</v>
+        <v>4286</v>
       </c>
     </row>
     <row r="190">
@@ -22322,16 +22769,16 @@
     </row>
     <row r="196">
       <c r="B196" s="0" t="s">
-        <v>1747</v>
+        <v>4272</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>1946</v>
+        <v>4279</v>
       </c>
       <c r="D196" s="0" t="s">
-        <v>2138</v>
+        <v>4287</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>2332</v>
+        <v>4294</v>
       </c>
     </row>
     <row r="197">
@@ -22746,16 +23193,16 @@
     </row>
     <row r="228">
       <c r="B228" s="0" t="s">
-        <v>1775</v>
+        <v>4273</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>1973</v>
+        <v>4280</v>
       </c>
       <c r="D228" s="0" t="s">
-        <v>2164</v>
+        <v>4288</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>2358</v>
+        <v>4295</v>
       </c>
     </row>
     <row r="229">
@@ -23010,16 +23457,16 @@
     </row>
     <row r="248">
       <c r="B248" s="0" t="s">
-        <v>1793</v>
+        <v>2168</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>1991</v>
+        <v>4281</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>2181</v>
+        <v>4289</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>2349</v>
+        <v>4296</v>
       </c>
     </row>
     <row r="249">
@@ -23130,7 +23577,7 @@
         <v>852</v>
       </c>
       <c r="H2" s="0">
-        <v>1323.9824791612721</v>
+        <v>1455.7459483791154</v>
       </c>
       <c r="I2" s="0">
         <v>3</v>
@@ -23139,13 +23586,13 @@
         <v>0</v>
       </c>
       <c r="K2" s="0">
-        <v>441.32749305375734</v>
+        <v>485.24864945970512</v>
       </c>
       <c r="L2" s="0">
-        <v>0.024120048116084352</v>
+        <v>0.026422969682480955</v>
       </c>
       <c r="M2" s="0">
-        <v>0.99493047970593629</v>
+        <v>0.99419939740028684</v>
       </c>
       <c r="O2" s="0" t="s">
         <v>872</v>
@@ -23168,7 +23615,7 @@
         <v>853</v>
       </c>
       <c r="H3" s="0">
-        <v>17729912.424342003</v>
+        <v>17795348.023966122</v>
       </c>
       <c r="I3" s="0">
         <v>969</v>
@@ -23177,7 +23624,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="0">
-        <v>18297.123244934988</v>
+        <v>18364.652243515091</v>
       </c>
       <c r="L3" s="0"/>
       <c r="M3" s="0"/>
@@ -23187,22 +23634,22 @@
     </row>
     <row r="4">
       <c r="B4" s="0" t="s">
-        <v>2376</v>
+        <v>4297</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>2572</v>
+        <v>4305</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>2772</v>
+        <v>4313</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>2967</v>
+        <v>4321</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>854</v>
       </c>
       <c r="H4" s="0">
-        <v>17731236.406821165</v>
+        <v>17796803.7699145</v>
       </c>
       <c r="I4" s="0">
         <v>972</v>
@@ -23331,16 +23778,16 @@
         <v>863</v>
       </c>
       <c r="I11" s="0">
-        <v>-30.334131513916908</v>
+        <v>-30.101077348622404</v>
       </c>
       <c r="J11" s="0">
-        <v>1.2247012300815641</v>
+        <v>1.5159386852486705</v>
       </c>
       <c r="K11" s="0">
-        <v>32.783533974080036</v>
+        <v>33.132954719119745</v>
       </c>
       <c r="L11" s="0">
-        <v>0.9996454089098431</v>
+        <v>0.99933253449569093</v>
       </c>
     </row>
     <row r="12">
@@ -23363,16 +23810,16 @@
         <v>864</v>
       </c>
       <c r="I12" s="0">
-        <v>-33.489843505087549</v>
+        <v>-33.498143295215897</v>
       </c>
       <c r="J12" s="0">
-        <v>-1.9310107610890839</v>
+        <v>-1.8811272613448295</v>
       </c>
       <c r="K12" s="0">
-        <v>29.627821982909378</v>
+        <v>29.735888772526238</v>
       </c>
       <c r="L12" s="0">
-        <v>0.99861775233148409</v>
+        <v>0.99872853203389722</v>
       </c>
     </row>
     <row r="13">
@@ -23395,16 +23842,16 @@
         <v>866</v>
       </c>
       <c r="I13" s="0">
-        <v>-32.445869318516309</v>
+        <v>-32.187462642662695</v>
       </c>
       <c r="J13" s="0">
-        <v>-0.95137514329141482</v>
+        <v>-0.63490379505739725</v>
       </c>
       <c r="K13" s="0">
-        <v>30.543119031933479</v>
+        <v>30.917655052547897</v>
       </c>
       <c r="L13" s="0">
-        <v>0.99983250791409772</v>
+        <v>0.99995042856678373</v>
       </c>
     </row>
     <row r="14">
@@ -23427,16 +23874,16 @@
         <v>864</v>
       </c>
       <c r="I14" s="0">
-        <v>-34.681993068183814</v>
+        <v>-34.98147029975533</v>
       </c>
       <c r="J14" s="0">
-        <v>-3.1557119911706479</v>
+        <v>-3.3970659465935</v>
       </c>
       <c r="K14" s="0">
-        <v>28.370569085842515</v>
+        <v>28.18733840656833</v>
       </c>
       <c r="L14" s="0">
-        <v>0.99404136584774749</v>
+        <v>0.99263603429726144</v>
       </c>
     </row>
     <row r="15">
@@ -23459,16 +23906,16 @@
         <v>866</v>
       </c>
       <c r="I15" s="0">
-        <v>-33.637952314525037</v>
+        <v>-33.670722957388499</v>
       </c>
       <c r="J15" s="0">
-        <v>-2.1760763733729789</v>
+        <v>-2.1508424803060677</v>
       </c>
       <c r="K15" s="0">
-        <v>29.28579956777908</v>
+        <v>29.369037996776363</v>
       </c>
       <c r="L15" s="0">
-        <v>0.99800865038317033</v>
+        <v>0.99808711962588337</v>
       </c>
     </row>
     <row r="16">
@@ -23491,16 +23938,16 @@
         <v>866</v>
       </c>
       <c r="I16" s="0">
-        <v>-30.482240323354414</v>
+        <v>-30.273657010795027</v>
       </c>
       <c r="J16" s="0">
-        <v>0.97963561779766906</v>
+        <v>1.2462234662874323</v>
       </c>
       <c r="K16" s="0">
-        <v>32.441511558949756</v>
+        <v>32.766103943369892</v>
       </c>
       <c r="L16" s="0">
-        <v>0.99981659103898457</v>
+        <v>0.99962505073948749</v>
       </c>
     </row>
     <row r="17">
@@ -23645,16 +24092,16 @@
     </row>
     <row r="27">
       <c r="B27" s="0" t="s">
-        <v>2394</v>
+        <v>4298</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>2590</v>
+        <v>4306</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>2789</v>
+        <v>4314</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>2985</v>
+        <v>4322</v>
       </c>
     </row>
     <row r="28">
@@ -24019,16 +24466,16 @@
     </row>
     <row r="54">
       <c r="B54" s="0" t="s">
-        <v>2416</v>
+        <v>4299</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>2615</v>
+        <v>4307</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>2812</v>
+        <v>4315</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>3008</v>
+        <v>4323</v>
       </c>
     </row>
     <row r="55">
@@ -24117,16 +24564,16 @@
     </row>
     <row r="61">
       <c r="B61" s="0" t="s">
-        <v>2422</v>
+        <v>4300</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>2622</v>
+        <v>4308</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>2819</v>
+        <v>4316</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>3015</v>
+        <v>4324</v>
       </c>
     </row>
     <row r="62">
@@ -25867,16 +26314,16 @@
     </row>
     <row r="189">
       <c r="B189" s="0" t="s">
-        <v>2517</v>
+        <v>4301</v>
       </c>
       <c r="C189" s="0" t="s">
-        <v>2717</v>
+        <v>4309</v>
       </c>
       <c r="D189" s="0" t="s">
-        <v>2913</v>
+        <v>4317</v>
       </c>
       <c r="E189" s="0" t="s">
-        <v>3108</v>
+        <v>4325</v>
       </c>
     </row>
     <row r="190">
@@ -25965,16 +26412,16 @@
     </row>
     <row r="196">
       <c r="B196" s="0" t="s">
-        <v>2523</v>
+        <v>4302</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>2723</v>
+        <v>4310</v>
       </c>
       <c r="D196" s="0" t="s">
-        <v>2919</v>
+        <v>4318</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>3113</v>
+        <v>4326</v>
       </c>
     </row>
     <row r="197">
@@ -26413,16 +26860,16 @@
     </row>
     <row r="228">
       <c r="B228" s="0" t="s">
-        <v>2551</v>
+        <v>4303</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>2751</v>
+        <v>4311</v>
       </c>
       <c r="D228" s="0" t="s">
-        <v>2946</v>
+        <v>4319</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>3140</v>
+        <v>4327</v>
       </c>
     </row>
     <row r="229">
@@ -26693,16 +27140,16 @@
     </row>
     <row r="248">
       <c r="B248" s="0" t="s">
-        <v>2569</v>
+        <v>4304</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>2769</v>
+        <v>4312</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>2964</v>
+        <v>4320</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>3157</v>
+        <v>4328</v>
       </c>
     </row>
     <row r="249">
@@ -26829,7 +27276,7 @@
         <v>852</v>
       </c>
       <c r="H2" s="0">
-        <v>0.62060630502975911</v>
+        <v>0.59762964886985892</v>
       </c>
       <c r="I2" s="0">
         <v>3</v>
@@ -26838,13 +27285,13 @@
         <v>0</v>
       </c>
       <c r="K2" s="0">
-        <v>0.20686876834325305</v>
+        <v>0.19920988295661965</v>
       </c>
       <c r="L2" s="0">
-        <v>0.14356420692638178</v>
+        <v>0.13794012459303581</v>
       </c>
       <c r="M2" s="0">
-        <v>0.93380494319205021</v>
+        <v>0.93734686813406598</v>
       </c>
       <c r="O2" s="0" t="s">
         <v>872</v>
@@ -26867,7 +27314,7 @@
         <v>853</v>
       </c>
       <c r="H3" s="0">
-        <v>1396.2800395463742</v>
+        <v>1399.4070047020255</v>
       </c>
       <c r="I3" s="0">
         <v>969</v>
@@ -26876,7 +27323,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="0">
-        <v>1.4409494732160724</v>
+        <v>1.4441764754406867</v>
       </c>
       <c r="L3" s="0"/>
       <c r="M3" s="0"/>
@@ -26886,22 +27333,22 @@
     </row>
     <row r="4">
       <c r="B4" s="0" t="s">
-        <v>3159</v>
+        <v>4329</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>3303</v>
+        <v>4337</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>1360</v>
+        <v>4341</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>3513</v>
+        <v>4348</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>854</v>
       </c>
       <c r="H4" s="0">
-        <v>1396.9006458514039</v>
+        <v>1400.0046343508952</v>
       </c>
       <c r="I4" s="0">
         <v>972</v>
@@ -27030,16 +27477,16 @@
         <v>863</v>
       </c>
       <c r="I11" s="0">
-        <v>-0.29536348970866766</v>
+        <v>-0.29337618014643713</v>
       </c>
       <c r="J11" s="0">
-        <v>-0.015301673224284107</v>
+        <v>-0.013000940223076851</v>
       </c>
       <c r="K11" s="0">
-        <v>0.26476014326009945</v>
+        <v>0.26737429970028342</v>
       </c>
       <c r="L11" s="0">
-        <v>0.99901402882546508</v>
+        <v>0.99939603493074125</v>
       </c>
     </row>
     <row r="12">
@@ -27062,16 +27509,16 @@
         <v>864</v>
       </c>
       <c r="I12" s="0">
-        <v>-0.24474623164125575</v>
+        <v>-0.24474617591125442</v>
       </c>
       <c r="J12" s="0">
-        <v>0.03531558484312769</v>
+        <v>0.035629064012105749</v>
       </c>
       <c r="K12" s="0">
-        <v>0.31537740132751113</v>
+        <v>0.31600430393546591</v>
       </c>
       <c r="L12" s="0">
-        <v>0.98825827148595791</v>
+        <v>0.98799049358964497</v>
       </c>
     </row>
     <row r="13">
@@ -27094,16 +27541,16 @@
         <v>866</v>
       </c>
       <c r="I13" s="0">
-        <v>-0.31279930014870649</v>
+        <v>-0.31199896107986108</v>
       </c>
       <c r="J13" s="0">
-        <v>-0.033308441930964161</v>
+        <v>-0.032195318395300765</v>
       </c>
       <c r="K13" s="0">
-        <v>0.24618241628677817</v>
+        <v>0.24760832428925955</v>
       </c>
       <c r="L13" s="0">
-        <v>0.99004673748979544</v>
+        <v>0.99102052310197009</v>
       </c>
     </row>
     <row r="14">
@@ -27126,16 +27573,16 @@
         <v>864</v>
       </c>
       <c r="I14" s="0">
-        <v>-0.2291556859146377</v>
+        <v>-0.23145603990216918</v>
       </c>
       <c r="J14" s="0">
-        <v>0.050617258067411797</v>
+        <v>0.0486300042351826</v>
       </c>
       <c r="K14" s="0">
-        <v>0.33039020204946129</v>
+        <v>0.32871604837253438</v>
       </c>
       <c r="L14" s="0">
-        <v>0.96671757485065968</v>
+        <v>0.97039880393448119</v>
       </c>
     </row>
     <row r="15">
@@ -27158,16 +27605,16 @@
         <v>866</v>
       </c>
       <c r="I15" s="0">
-        <v>-0.29720816368732944</v>
+        <v>-0.29870823367491239</v>
       </c>
       <c r="J15" s="0">
-        <v>-0.018006768706680054</v>
+        <v>-0.019194378172223914</v>
       </c>
       <c r="K15" s="0">
-        <v>0.26119462627396933</v>
+        <v>0.26031947733046457</v>
       </c>
       <c r="L15" s="0">
-        <v>0.99838302495531839</v>
+        <v>0.99805076485310651</v>
       </c>
     </row>
     <row r="16">
@@ -27190,16 +27637,16 @@
         <v>866</v>
       </c>
       <c r="I16" s="0">
-        <v>-0.34782542175474152</v>
+        <v>-0.34733823791009527</v>
       </c>
       <c r="J16" s="0">
-        <v>-0.068624026774091851</v>
+        <v>-0.067824382407406514</v>
       </c>
       <c r="K16" s="0">
-        <v>0.21057736820655781</v>
+        <v>0.21168947309528224</v>
       </c>
       <c r="L16" s="0">
-        <v>0.92194539736262937</v>
+        <v>0.92461860139212537</v>
       </c>
     </row>
     <row r="17">
@@ -27344,16 +27791,16 @@
     </row>
     <row r="27">
       <c r="B27" s="0" t="s">
-        <v>3175</v>
+        <v>4330</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>3317</v>
+        <v>3210</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>3429</v>
+        <v>4342</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>3204</v>
+        <v>4349</v>
       </c>
     </row>
     <row r="28">
@@ -27718,16 +28165,16 @@
     </row>
     <row r="54">
       <c r="B54" s="0" t="s">
-        <v>3194</v>
+        <v>4331</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>3331</v>
+        <v>4338</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>3440</v>
+        <v>4343</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>3537</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="55">
@@ -27816,16 +28263,16 @@
     </row>
     <row r="61">
       <c r="B61" s="0" t="s">
-        <v>3199</v>
+        <v>4332</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>3336</v>
+        <v>938</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>3444</v>
+        <v>4344</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>3540</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="62">
@@ -29566,16 +30013,16 @@
     </row>
     <row r="189">
       <c r="B189" s="0" t="s">
-        <v>3268</v>
+        <v>4333</v>
       </c>
       <c r="C189" s="0" t="s">
-        <v>3388</v>
+        <v>4339</v>
       </c>
       <c r="D189" s="0" t="s">
-        <v>3487</v>
+        <v>4345</v>
       </c>
       <c r="E189" s="0" t="s">
-        <v>3583</v>
+        <v>4351</v>
       </c>
     </row>
     <row r="190">
@@ -29664,16 +30111,16 @@
     </row>
     <row r="196">
       <c r="B196" s="0" t="s">
-        <v>3271</v>
+        <v>4334</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>3392</v>
+        <v>3498</v>
       </c>
       <c r="D196" s="0" t="s">
-        <v>3491</v>
+        <v>4346</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>3587</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="197">
@@ -30112,16 +30559,16 @@
     </row>
     <row r="228">
       <c r="B228" s="0" t="s">
-        <v>3217</v>
+        <v>4335</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>2307</v>
+        <v>4340</v>
       </c>
       <c r="D228" s="0" t="s">
-        <v>3408</v>
+        <v>1874</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>3603</v>
+        <v>4352</v>
       </c>
     </row>
     <row r="229">
@@ -30392,16 +30839,16 @@
     </row>
     <row r="248">
       <c r="B248" s="0" t="s">
-        <v>3301</v>
+        <v>4336</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>3417</v>
+        <v>3300</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>3511</v>
+        <v>4347</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>3612</v>
+        <v>4353</v>
       </c>
     </row>
     <row r="249">
